--- a/templates/reg_ref_decir.xlsx
+++ b/templates/reg_ref_decir.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89C06429-368E-4A94-AA16-DDB7856B3DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDA02F6-24C8-48FA-A5F5-825D546A12E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{775496B6-CC82-4041-A39E-C72AA7906EDB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Dia</t>
   </si>
@@ -61,12 +61,6 @@
   </si>
   <si>
     <t>Núcleo Adm. e Financeiro</t>
-  </si>
-  <si>
-    <t>Responsável O Crisina</t>
-  </si>
-  <si>
-    <t>Responsável O Sol</t>
   </si>
 </sst>
 </file>
@@ -1767,14 +1761,10 @@
       <c r="N52" s="35"/>
     </row>
     <row r="53" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C53" s="36" t="s">
-        <v>9</v>
-      </c>
+      <c r="C53" s="36"/>
       <c r="D53" s="37"/>
       <c r="E53" s="38"/>
-      <c r="L53" s="36" t="s">
-        <v>10</v>
-      </c>
+      <c r="L53" s="36"/>
       <c r="M53" s="37"/>
       <c r="N53" s="38"/>
     </row>

--- a/templates/reg_ref_decir.xlsx
+++ b/templates/reg_ref_decir.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDA02F6-24C8-48FA-A5F5-825D546A12E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9180772B-6931-4A31-B71A-09A3B6C7000F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{775496B6-CC82-4041-A39E-C72AA7906EDB}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,6 +104,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -494,92 +502,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
@@ -587,6 +524,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -594,6 +540,69 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1070,7 +1079,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:P53"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
@@ -1086,690 +1095,810 @@
   <sheetData>
     <row r="1" spans="2:16" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
     </row>
     <row r="7" spans="2:16" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="21" t="s">
+      <c r="D8" s="23"/>
+      <c r="E8" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="22" t="s">
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22" t="s">
+      <c r="I8" s="33"/>
+      <c r="J8" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="22"/>
-      <c r="L8" s="23" t="s">
+      <c r="K8" s="33"/>
+      <c r="L8" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="25"/>
-      <c r="N8" s="19" t="s">
+      <c r="M8" s="36"/>
+      <c r="N8" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="O8" s="20"/>
-      <c r="P8" s="2"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="1"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B9" s="4"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="30"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="25"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B10" s="6"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="27"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="18"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B11" s="6"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="27"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="18"/>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B12" s="6"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="27"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="18"/>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B13" s="6"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="27"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="18"/>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B14" s="6"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="27"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="18"/>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B15" s="6"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="27"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="18"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B16" s="6"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="27"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="18"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="6"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="27"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="18"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="6"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="27"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="18"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B19" s="6"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="27"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="31"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="18"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B20" s="6"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="27"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="18"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="6"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="27"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="18"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="6"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="27"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="18"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="27"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="18"/>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B24" s="6"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="27"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="18"/>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B25" s="6"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="27"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="18"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B26" s="6"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="27"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="18"/>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B27" s="6"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="27"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="31"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="18"/>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B28" s="6"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="27"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="18"/>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B29" s="6"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="27"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="18"/>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B30" s="6"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="27"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="31"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="18"/>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B31" s="6"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="27"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="18"/>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B32" s="6"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="27"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="18"/>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B33" s="6"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="27"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="18"/>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B34" s="6"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="27"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="31"/>
+      <c r="J34" s="31"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="31"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="18"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B35" s="6"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="27"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
+      <c r="J35" s="31"/>
+      <c r="K35" s="31"/>
+      <c r="L35" s="31"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="18"/>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B36" s="6"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="27"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
+      <c r="J36" s="31"/>
+      <c r="K36" s="31"/>
+      <c r="L36" s="31"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="18"/>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B37" s="6"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="27"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="18"/>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B38" s="6"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="14"/>
-      <c r="N38" s="14"/>
-      <c r="O38" s="27"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="31"/>
+      <c r="K38" s="31"/>
+      <c r="L38" s="31"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="18"/>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B39" s="8"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="26"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="28"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="30"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="12"/>
     </row>
     <row r="40" spans="2:15" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="E41" s="10"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="24"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="21"/>
+      <c r="K41" s="21"/>
+      <c r="L41" s="37"/>
     </row>
     <row r="42" spans="2:15" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="E43" s="10"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="24"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="21"/>
+      <c r="K43" s="21"/>
+      <c r="L43" s="37"/>
     </row>
     <row r="44" spans="2:15" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="45" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B45" s="3"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="32"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="31"/>
-      <c r="M45" s="32"/>
-      <c r="N45" s="33"/>
-      <c r="O45" s="3"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="8"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="7"/>
+      <c r="N45" s="8"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B46" s="3"/>
-      <c r="C46" s="34"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="34"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="35"/>
-      <c r="O46" s="3"/>
+      <c r="C46" s="9"/>
+      <c r="E46" s="10"/>
+      <c r="L46" s="9"/>
+      <c r="N46" s="10"/>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B47" s="3"/>
-      <c r="C47" s="34"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="35"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="34"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="35"/>
-      <c r="O47" s="3"/>
+      <c r="C47" s="9"/>
+      <c r="E47" s="10"/>
+      <c r="L47" s="9"/>
+      <c r="N47" s="10"/>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B48" s="3"/>
-      <c r="C48" s="36" t="s">
+      <c r="C48" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D48" s="37"/>
-      <c r="E48" s="38"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="36" t="s">
+      <c r="D48" s="15"/>
+      <c r="E48" s="16"/>
+      <c r="L48" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="M48" s="37"/>
-      <c r="N48" s="38"/>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="2:15" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C50" s="31"/>
-      <c r="D50" s="32"/>
-      <c r="E50" s="33"/>
-      <c r="L50" s="31"/>
-      <c r="M50" s="32"/>
-      <c r="N50" s="33"/>
-    </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C51" s="34"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="35"/>
-      <c r="L51" s="34"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="35"/>
-    </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C52" s="34"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="35"/>
-      <c r="L52" s="34"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="35"/>
-    </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C53" s="36"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="38"/>
-      <c r="L53" s="36"/>
-      <c r="M53" s="37"/>
-      <c r="N53" s="38"/>
+      <c r="M48" s="15"/>
+      <c r="N48" s="16"/>
+    </row>
+    <row r="49" spans="3:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C50" s="6"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="8"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="7"/>
+      <c r="N50" s="8"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C51" s="9"/>
+      <c r="E51" s="10"/>
+      <c r="L51" s="9"/>
+      <c r="N51" s="10"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C52" s="9"/>
+      <c r="E52" s="10"/>
+      <c r="L52" s="9"/>
+      <c r="N52" s="10"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C53" s="14"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="16"/>
+      <c r="L53" s="14"/>
+      <c r="M53" s="15"/>
+      <c r="N53" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="199">
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E41:K41"/>
+    <mergeCell ref="E43:K43"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="E34:G34"/>
     <mergeCell ref="N39:O39"/>
     <mergeCell ref="B6:O6"/>
     <mergeCell ref="C48:E48"/>
@@ -1794,181 +1923,6 @@
     <mergeCell ref="N24:O24"/>
     <mergeCell ref="N25:O25"/>
     <mergeCell ref="N26:O26"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="E41:K41"/>
-    <mergeCell ref="E43:K43"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="E14:G14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C9:C39">
